--- a/04_DESIGN_TABLES/DesignTable_5505_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5505_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AM4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,145 @@
       <c r="AM3" t="inlineStr">
         <is>
           <t>5505-04-04-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>5505-08-08-FG</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.61265</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>5505-08-08-FG</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>45 deg Female Pipe Elbow, 1/2-14 NPTF (female) x 1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>5505</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5505-08-08 (differs by -FG suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_5505-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: N2_1@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "N LGTH" = "0.940" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - A1 female port leg: crossing to the port face; own STEP: port face 0.94 (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); N2_2@DRIVE: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "N1 LGTH" = "0.940" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - A2 female port leg: crossing to the port face; own STEP: port face 0.94 (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); W@HEX: Brennan TFA catalog p.32 table TFA-p032-t03 "5505-FG FP-FP 45 DEG ELBOW" row 5505-08-08-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 716.1, page verified True) [Brennan = yes 2026-10-18] - forged body flats; own STEP: A/F 1.062 on both legs (C_ownstep/measure/5505-08-08-FG.txt (forged.py NPTFF legs at 45 / 180 deg)); TAPDRILL1@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); TAPDRILL2@BORE: end library: tap drill of the -08 female NPTF port = 0.7 (gen_straight2 FPT[8] = templates/DesignTable_2405_SW2.xlsx TAPDRILL@BORE_A, row 2405-08-08) [Q-TRANSFER-ENDLIB yes 2026-10-08: new masters take tap drills from the end library] (own STEP: Brennan port drill 0.718); THDMAJ_A1@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A2@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; PORTDEPTH@BORE: Brennan port depth -08 = 0.750 measured on this part's own STEP 09_STEP_FILES/BRENNAN_5505-08-08-FG.stp (forged.py: taper depth from the face 0.75 on both ports, mouth 0.049; brennan_port_depths.run 0.7500; C_ownstep/measure/5505-08-08-FG.txt) = the -08 value of gen_tee ANGLED_P1_NOTE (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18: the MS51503 P1 0.90 does not fit the 0.94 leg of the 45 deg elbow) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPTF port on the 45 deg leg (Q-NEW-ANGLEDFEMALE): the 5504 / 1502 forged female leg turned to the 135 deg axis - hex arm to 0.26 short of the port face, round collar of dia = the hex flats, tap drill from the port face (pocket), tapered helical thread over the port depth (Brennan 1504-06-06-FG / 5505-08-08-FG / 5503-16-16-FG STEPs: collar 0.26 at the flats dia on the 45 deg leg, the same end as on the axis legs); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; leg 1 port depth 0.750 = the row PORTDEPTH instead of MS51503 P1 0.9 (which does not fit the 0.94 leg): the port depth Brennan draws for -08: 0.750 (Brennan 1502 / 2505 / 2606 / 5502 / 5504 / 5505 / 5603 / 5605 / 5652 -08 STEPs and 5 more); leg 2 port depth 0.750 = the row PORTDEPTH instead of MS51503 P1 0.9 (which does not fit the 0.94 leg): the port depth Brennan draws for -08: 0.750 (Brennan 1502 / 2505 / 2606 / 5502 / 5504 / 5505 / 5603 / 5605 / 5652 -08 STEPs and 5 more); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5505-08-08 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 5505-8-8 (plain): N2 0.94 / 0.94 W 1.13 TAPDRILL 0.70 (legs agree; flats differ: forged 1.062)</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>5505-08-08-FG</t>
         </is>
       </c>
     </row>
